--- a/assets/me3.xlsx
+++ b/assets/me3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W256"/>
+  <dimension ref="A1:W260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18255,6 +18255,298 @@
         <v>64.48999999999999</v>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>255</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>11/10/2024</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>186.9455555555556</v>
+      </c>
+      <c r="D257" t="n">
+        <v>164.75</v>
+      </c>
+      <c r="E257" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="F257" t="n">
+        <v>143</v>
+      </c>
+      <c r="G257" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="H257" t="n">
+        <v>134</v>
+      </c>
+      <c r="I257" t="n">
+        <v>67.83799999999999</v>
+      </c>
+      <c r="J257" t="n">
+        <v>62</v>
+      </c>
+      <c r="K257" t="n">
+        <v>125</v>
+      </c>
+      <c r="L257" t="n">
+        <v>391.5</v>
+      </c>
+      <c r="M257" t="n">
+        <v>120</v>
+      </c>
+      <c r="N257" t="n">
+        <v>244</v>
+      </c>
+      <c r="O257" t="n">
+        <v>199</v>
+      </c>
+      <c r="P257" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q257" t="n">
+        <v>180</v>
+      </c>
+      <c r="R257" t="n">
+        <v>99</v>
+      </c>
+      <c r="S257" t="n">
+        <v>160</v>
+      </c>
+      <c r="T257" t="n">
+        <v>0.3192307692307693</v>
+      </c>
+      <c r="U257" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="V257" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="W257" t="n">
+        <v>64.48999999999999</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>14/10/2024</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>177.8666666666667</v>
+      </c>
+      <c r="D258" t="n">
+        <v>158.6666666666667</v>
+      </c>
+      <c r="E258" t="n">
+        <v>151.75</v>
+      </c>
+      <c r="F258" t="n">
+        <v>143</v>
+      </c>
+      <c r="G258" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="H258" t="n">
+        <v>134</v>
+      </c>
+      <c r="I258" t="n">
+        <v>67.83799999999999</v>
+      </c>
+      <c r="J258" t="n">
+        <v>62</v>
+      </c>
+      <c r="K258" t="n">
+        <v>125</v>
+      </c>
+      <c r="L258" t="n">
+        <v>360</v>
+      </c>
+      <c r="M258" t="n">
+        <v>120</v>
+      </c>
+      <c r="N258" t="n">
+        <v>244</v>
+      </c>
+      <c r="O258" t="n">
+        <v>199</v>
+      </c>
+      <c r="P258" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q258" t="n">
+        <v>180</v>
+      </c>
+      <c r="R258" t="n">
+        <v>99</v>
+      </c>
+      <c r="S258" t="n">
+        <v>160</v>
+      </c>
+      <c r="T258" t="n">
+        <v>0.3192307692307693</v>
+      </c>
+      <c r="U258" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="V258" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="W258" t="n">
+        <v>64.48999999999999</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>257</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>15/10/2024</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="D259" t="n">
+        <v>155.25</v>
+      </c>
+      <c r="E259" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="F259" t="n">
+        <v>143</v>
+      </c>
+      <c r="G259" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="H259" t="n">
+        <v>134</v>
+      </c>
+      <c r="I259" t="n">
+        <v>67.83799999999999</v>
+      </c>
+      <c r="J259" t="n">
+        <v>62</v>
+      </c>
+      <c r="K259" t="n">
+        <v>125</v>
+      </c>
+      <c r="L259" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="M259" t="n">
+        <v>120</v>
+      </c>
+      <c r="N259" t="n">
+        <v>244</v>
+      </c>
+      <c r="O259" t="n">
+        <v>199</v>
+      </c>
+      <c r="P259" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q259" t="n">
+        <v>180</v>
+      </c>
+      <c r="R259" t="n">
+        <v>99</v>
+      </c>
+      <c r="S259" t="n">
+        <v>160</v>
+      </c>
+      <c r="T259" t="n">
+        <v>0.3192307692307693</v>
+      </c>
+      <c r="U259" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="V259" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="W259" t="n">
+        <v>64.48999999999999</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>258</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>16/10/2024</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="D260" t="n">
+        <v>160</v>
+      </c>
+      <c r="E260" t="n">
+        <v>133.5</v>
+      </c>
+      <c r="F260" t="n">
+        <v>143</v>
+      </c>
+      <c r="G260" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="H260" t="n">
+        <v>134</v>
+      </c>
+      <c r="I260" t="n">
+        <v>67.83799999999999</v>
+      </c>
+      <c r="J260" t="n">
+        <v>62</v>
+      </c>
+      <c r="K260" t="n">
+        <v>125</v>
+      </c>
+      <c r="L260" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="M260" t="n">
+        <v>120</v>
+      </c>
+      <c r="N260" t="n">
+        <v>244</v>
+      </c>
+      <c r="O260" t="n">
+        <v>199</v>
+      </c>
+      <c r="P260" t="n">
+        <v>181</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>180</v>
+      </c>
+      <c r="R260" t="n">
+        <v>99</v>
+      </c>
+      <c r="S260" t="n">
+        <v>160</v>
+      </c>
+      <c r="T260" t="n">
+        <v>0.3192307692307693</v>
+      </c>
+      <c r="U260" t="n">
+        <v>64.48999999999999</v>
+      </c>
+      <c r="V260" t="n">
+        <v>118.25</v>
+      </c>
+      <c r="W260" t="n">
+        <v>64.48999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
